--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747650</v>
+        <v>122747643</v>
       </c>
       <c r="B2" t="n">
-        <v>105335</v>
+        <v>92213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758536</v>
+        <v>758364</v>
       </c>
       <c r="R2" t="n">
-        <v>7225997</v>
+        <v>7226116</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747643</v>
+        <v>122747650</v>
       </c>
       <c r="B3" t="n">
-        <v>92110</v>
+        <v>105438</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758364</v>
+        <v>758536</v>
       </c>
       <c r="R3" t="n">
-        <v>7226116</v>
+        <v>7225997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747643</v>
       </c>
       <c r="B2" t="n">
-        <v>92213</v>
+        <v>92217</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747650</v>
       </c>
       <c r="B3" t="n">
-        <v>105438</v>
+        <v>105446</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122747650</v>
       </c>
       <c r="B3" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747643</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747650</v>
       </c>
       <c r="B3" t="n">
-        <v>105448</v>
+        <v>105456</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747643</v>
+        <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>105456</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758364</v>
+        <v>758536</v>
       </c>
       <c r="R2" t="n">
-        <v>7226116</v>
+        <v>7225997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747650</v>
+        <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>105456</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758536</v>
+        <v>758364</v>
       </c>
       <c r="R3" t="n">
-        <v>7225997</v>
+        <v>7226116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747650</v>
+        <v>122747643</v>
       </c>
       <c r="B2" t="n">
-        <v>105456</v>
+        <v>92228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758536</v>
+        <v>758364</v>
       </c>
       <c r="R2" t="n">
-        <v>7225997</v>
+        <v>7226116</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747643</v>
+        <v>122747650</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>105459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758364</v>
+        <v>758536</v>
       </c>
       <c r="R3" t="n">
-        <v>7226116</v>
+        <v>7225997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747643</v>
+        <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>92228</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758364</v>
+        <v>758536</v>
       </c>
       <c r="R2" t="n">
-        <v>7226116</v>
+        <v>7225997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747650</v>
+        <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>105459</v>
+        <v>92230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758536</v>
+        <v>758364</v>
       </c>
       <c r="R3" t="n">
-        <v>7225997</v>
+        <v>7226116</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>106204</v>
+        <v>106207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>93169</v>
+        <v>93172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>106207</v>
+        <v>106215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>93172</v>
+        <v>93178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>106215</v>
+        <v>106226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>93178</v>
+        <v>93188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>106226</v>
+        <v>106227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747643</v>
       </c>
       <c r="B3" t="n">
-        <v>93188</v>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53271-2024 artfynd.xlsx
+++ b/artfynd/A 53271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747650</v>
       </c>
       <c r="B2" t="n">
-        <v>106227</v>
+        <v>106228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
